--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_individual_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_individual_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008429030597149695</v>
       </c>
       <c r="C2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>12385893</v>
+        <v>4178265</v>
       </c>
       <c r="L2" t="n">
-        <v>4768876</v>
+        <v>1546786</v>
       </c>
       <c r="M2" t="n">
-        <v>857216</v>
+        <v>285695</v>
       </c>
       <c r="N2" t="n">
-        <v>19134</v>
+        <v>6589</v>
       </c>
       <c r="O2" t="n">
-        <v>524487</v>
+        <v>174756</v>
       </c>
       <c r="P2" t="n">
-        <v>11349</v>
+        <v>4083</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999010562896729</v>
+        <v>0.9998332262039185</v>
       </c>
       <c r="R2" t="n">
-        <v>0.720833420753479</v>
+        <v>0.7155470252037048</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5319174528121948</v>
+        <v>0.5362794399261475</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4005760848522186</v>
+        <v>0.4023079872131348</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04472337290644646</v>
+        <v>0.04665670543909073</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4013242125511169</v>
+        <v>0.4048295319080353</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4516116082668304</v>
+        <v>0.4548290073871613</v>
       </c>
       <c r="X2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566799402236938</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112439155578613</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581776022911072</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626315712928772</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020464420318604</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002021254280242989</v>
       </c>
       <c r="C3" t="n">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="D3" t="n">
-        <v>12385893</v>
+        <v>4178265</v>
       </c>
       <c r="E3" t="n">
-        <v>2582222</v>
+        <v>807911</v>
       </c>
       <c r="F3" t="n">
-        <v>109609</v>
+        <v>35171</v>
       </c>
       <c r="G3" t="n">
-        <v>12500</v>
+        <v>3991</v>
       </c>
       <c r="H3" t="n">
-        <v>10875</v>
+        <v>3111</v>
       </c>
       <c r="I3" t="n">
-        <v>503</v>
+        <v>176</v>
       </c>
       <c r="J3" t="n">
-        <v>30047992</v>
+        <v>10015569</v>
       </c>
       <c r="K3" t="n">
-        <v>29090216</v>
+        <v>9639903</v>
       </c>
       <c r="L3" t="n">
-        <v>35013370</v>
+        <v>11727903</v>
       </c>
       <c r="M3" t="n">
-        <v>44910772</v>
+        <v>14973035</v>
       </c>
       <c r="N3" t="n">
-        <v>48312906</v>
+        <v>16105837</v>
       </c>
       <c r="O3" t="n">
-        <v>46679460</v>
+        <v>15563500</v>
       </c>
       <c r="P3" t="n">
-        <v>48395173</v>
+        <v>16131405</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8201634287834167</v>
+        <v>0.8308833837509155</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4876718819141388</v>
+        <v>0.473864883184433</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3066648542881012</v>
+        <v>0.3065002262592316</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07160981744527817</v>
+        <v>0.07392655313014984</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3434898257255554</v>
+        <v>0.3432120084762573</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01957243867218494</v>
+        <v>0.02112249843776226</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>593526</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25572</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20336</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30049866</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33232195</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38343158</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45797268</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48631528</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47312358</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48369192</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576433300971985</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.910033106803894</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577702045440674</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.662115752696991</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016677737236023</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03189760997342238</v>
       </c>
       <c r="C4" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>4264548</v>
+        <v>1473237</v>
       </c>
       <c r="E4" t="n">
-        <v>4768876</v>
+        <v>1546786</v>
       </c>
       <c r="F4" t="n">
-        <v>575750</v>
+        <v>189265</v>
       </c>
       <c r="G4" t="n">
-        <v>66671</v>
+        <v>21786</v>
       </c>
       <c r="H4" t="n">
-        <v>100985</v>
+        <v>32450</v>
       </c>
       <c r="I4" t="n">
-        <v>1971</v>
+        <v>633</v>
       </c>
       <c r="J4" t="n">
-        <v>1874</v>
+        <v>1053</v>
       </c>
       <c r="K4" t="n">
-        <v>4796846</v>
+        <v>1660995</v>
       </c>
       <c r="L4" t="n">
-        <v>4196568</v>
+        <v>1337505</v>
       </c>
       <c r="M4" t="n">
-        <v>1282742</v>
+        <v>424445</v>
       </c>
       <c r="N4" t="n">
-        <v>408696</v>
+        <v>134634</v>
       </c>
       <c r="O4" t="n">
-        <v>782404</v>
+        <v>256922</v>
       </c>
       <c r="P4" t="n">
-        <v>13781</v>
+        <v>4894</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999505281448364</v>
+        <v>0.9999166131019592</v>
       </c>
       <c r="R4" t="n">
-        <v>0.767297089099884</v>
+        <v>0.7689142227172852</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5088346004486084</v>
+        <v>0.5031439065933228</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3473854660987854</v>
+        <v>0.3479290902614594</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05505965277552605</v>
+        <v>0.0572080984711647</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3701616227626801</v>
+        <v>0.3714830279350281</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03751884400844574</v>
+        <v>0.04037018492817879</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>611398</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>248302</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16438</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>654867</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>866780</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>396246</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>90074</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149506</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571613669395447</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106380939483643</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579738140106201</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623735427856445</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018570184707642</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c r="D5" t="n">
-        <v>393723</v>
+        <v>138793</v>
       </c>
       <c r="E5" t="n">
-        <v>1195961</v>
+        <v>392829</v>
       </c>
       <c r="F5" t="n">
-        <v>857216</v>
+        <v>285695</v>
       </c>
       <c r="G5" t="n">
-        <v>105208</v>
+        <v>35057</v>
       </c>
       <c r="H5" t="n">
-        <v>239703</v>
+        <v>78380</v>
       </c>
       <c r="I5" t="n">
-        <v>3237</v>
+        <v>1241</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2715845</v>
+        <v>850437</v>
       </c>
       <c r="L5" t="n">
-        <v>5009986</v>
+        <v>1717406</v>
       </c>
       <c r="M5" t="n">
-        <v>1938070</v>
+        <v>646425</v>
       </c>
       <c r="N5" t="n">
-        <v>248064</v>
+        <v>82540</v>
       </c>
       <c r="O5" t="n">
-        <v>1002449</v>
+        <v>334422</v>
       </c>
       <c r="P5" t="n">
-        <v>568497</v>
+        <v>189218</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999617338180542</v>
+        <v>0.999935507774353</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8466446995735168</v>
+        <v>0.8462036848068237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8120681643486023</v>
+        <v>0.8129218816757202</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9342541098594666</v>
+        <v>0.9344215393066406</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9865936636924744</v>
+        <v>0.9867005944252014</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9635661244392395</v>
+        <v>0.9637869596481323</v>
       </c>
       <c r="W5" t="n">
-        <v>0.988114058971405</v>
+        <v>0.9881128668785095</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23984</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254565</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29795</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87330</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>639659</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>879774</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397573</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90282</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150147</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735750555992126</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643478989601135</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837958812713623</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963183999061584</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938832521438599</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983758926391602</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="D6" t="n">
-        <v>70588</v>
+        <v>24628</v>
       </c>
       <c r="E6" t="n">
-        <v>79633</v>
+        <v>25635</v>
       </c>
       <c r="F6" t="n">
-        <v>71673</v>
+        <v>23704</v>
       </c>
       <c r="G6" t="n">
-        <v>19134</v>
+        <v>6589</v>
       </c>
       <c r="H6" t="n">
-        <v>25236</v>
+        <v>8243</v>
       </c>
       <c r="I6" t="n">
-        <v>795</v>
+        <v>264</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19318</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>16016</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32584</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20921</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>583</v>
+        <v>335</v>
       </c>
       <c r="D7" t="n">
-        <v>62266</v>
+        <v>22194</v>
       </c>
       <c r="E7" t="n">
-        <v>301629</v>
+        <v>99083</v>
       </c>
       <c r="F7" t="n">
-        <v>449197</v>
+        <v>150621</v>
       </c>
       <c r="G7" t="n">
-        <v>181499</v>
+        <v>59609</v>
       </c>
       <c r="H7" t="n">
-        <v>524487</v>
+        <v>174756</v>
       </c>
       <c r="I7" t="n">
-        <v>7275</v>
+        <v>2580</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2430</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88798</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22710</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>717</v>
+        <v>415</v>
       </c>
       <c r="D8" t="n">
-        <v>5721</v>
+        <v>2143</v>
       </c>
       <c r="E8" t="n">
-        <v>37123</v>
+        <v>12047</v>
       </c>
       <c r="F8" t="n">
-        <v>76513</v>
+        <v>25684</v>
       </c>
       <c r="G8" t="n">
-        <v>42818</v>
+        <v>14191</v>
       </c>
       <c r="H8" t="n">
-        <v>405605</v>
+        <v>134738</v>
       </c>
       <c r="I8" t="n">
-        <v>11349</v>
+        <v>4083</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
